--- a/inst/resources/tool_kii_wash_service_provider_iphra_v2.xlsx
+++ b/inst/resources/tool_kii_wash_service_provider_iphra_v2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1170" yWindow="720" windowWidth="14535" windowHeight="15480" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -721,6 +721,21 @@
           <t>start</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>début</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>البداية</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>inicio</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>start</t>
@@ -741,6 +756,21 @@
           <t>end</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>fin</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>النهاية</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>fin</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>end</t>
@@ -761,6 +791,21 @@
           <t>today</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>aujourd’hui</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>اليوم</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>hoy</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>today</t>
@@ -781,6 +826,21 @@
           <t>deviceid</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>identifiant de l’appareil</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>معرّف الجهاز</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>identificador del dispositivo</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>deviceid</t>
@@ -801,6 +861,21 @@
           <t>audit</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>journal d’audit</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>سجل التدقيق</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>registro de auditoría</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>audit</t>
@@ -826,7 +901,21 @@
           <t>enumerator</t>
         </is>
       </c>
-      <c r="D7" s="8" t="n"/>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Veuillez indiquer l’identifiant de l’enquêteur</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>يرجى تحديد معرف الباحث الميداني</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Por favor indique el identificador del encuestador</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>Please specify enumerator ID</t>
@@ -850,6 +939,51 @@
       <c r="C8" t="inlineStr">
         <is>
           <t>consent</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Je m’appelle ___ et je travaille pour REACH Initiative, une organisation sœur d’ACTED, une organisation internationale à but non lucratif opérant dans cette zone.
+Nous réalisons une évaluation d’urgence afin de mieux comprendre les besoins et priorités en matière d’eau, d’assainissement et d’hygiène de la population.
+Nous souhaiterions vous poser quelques questions sur votre perception des besoins de la communauté et des services WASH. Vos réponses seront partagées avec les acteurs humanitaires afin d’orienter leurs interventions.
+L’entretien durera environ 30 minutes.
+Il n’y a aucun avantage direct à participer, et vos réponses n’affecteront pas votre accès à l’aide. Votre participation est volontaire et vous pouvez arrêter à tout moment. Toutes vos réponses resteront confidentielles.
+Acceptez-vous de participer à cet entretien ? [OUI / NON]</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sélectionnez une réponse</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>أنا ___ وأعمل مع مبادرة REACH، وهي منظمة شريكة لـ ACTED، وهي منظمة دولية غير ربحية تعمل في هذه المنطقة.
+نقوم بإجراء تقييم طارئ لفهم احتياجات وأولويات المياه والصرف الصحي والنظافة لدى السكان.
+نود أن نطرح عليك بعض الأسئلة حول تصورك لاحتياجات المجتمع وخدمات المياه والصرف الصحي والنظافة. سيتم مشاركة إجاباتك مع الجهات الإنسانية لدعم تخطيط أنشطتها.
+ستستغرق المقابلة حوالي 30 دقيقة.
+لا توجد أي فائدة مباشرة من المشاركة، ولن تؤثر إجاباتك على حصولك على المساعدات. مشاركتك طوعية ويمكنك التوقف في أي وقت. سيتم الحفاظ على سرية جميع إجاباتك.
+هل توافق على المشاركة في هذه المقابلة؟ [نعم / لا]</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>اختر إجابة واحدة</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Soy ___ y trabajo para REACH Initiative, una organización asociada a ACTED, una organización internacional sin fines de lucro que trabaja en esta zona.
+Estamos realizando una evaluación de emergencia para comprender las necesidades y prioridades de agua, saneamiento e higiene de la población.
+Nos gustaría hacerle algunas preguntas sobre su percepción de las necesidades de la comunidad y los servicios WASH. Sus respuestas serán compartidas con actores humanitarios para orientar sus actividades.
+La entrevista durará aproximadamente 30 minutos.
+No hay ningún beneficio directo por participar, y sus respuestas no afectarán su acceso a la ayuda. Su participación es voluntaria y puede detener la entrevista en cualquier momento. Todas sus respuestas serán confidenciales.
+¿Acepta participar en esta entrevista? [SÍ / NO]</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Seleccione una opción</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -899,7 +1033,21 @@
           <t>recording_consent</t>
         </is>
       </c>
-      <c r="D10" s="3" t="n"/>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Consentez-vous à ce que cet entretien soit enregistré afin de faciliter la vérification des notes ?</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>هل توافق على تسجيل هذه المقابلة للمساعدة في مراجعة الملاحظات والتحقق منها؟</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>¿Acepta que esta entrevista sea grabada para ayudar a revisar y verificar las notas?</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t xml:space="preserve">Do you consent to being recorded for this interview? This is to help us with checking and verifying interview notes. </t>
@@ -947,6 +1095,21 @@
           <t>name</t>
         </is>
       </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Nom du répondant (facultatif)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>اسم المشارك (اختياري)</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Nombre del encuestado (opcional)</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>What is the respondent's name? (optional)</t>
@@ -972,7 +1135,32 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Quel est le sexe du répondant?</t>
+          <t>Sexe du répondant</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sélectionnez une réponse</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>جنس المشارك</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>اختر إجابة واحدة</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sexo del encuestado</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Seleccione una opción</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1005,6 +1193,21 @@
           <t>position</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Fonction du répondant</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>وظيفة المشارك</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Cargo del encuestado</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>What is the respondent's position?</t>
@@ -1030,6 +1233,21 @@
           <t>contact</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Coordonnées du répondant (facultatif)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>معلومات الاتصال الخاصة بالمشارك (اختياري)</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Información de contacto del encuestado (opcional)</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>What is the respondent's contact information? (optional)</t>
@@ -1055,7 +1273,21 @@
           <t>programs_wash</t>
         </is>
       </c>
-      <c r="D16" s="2" t="n"/>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Quels types d’activités ou de programmes en eau, assainissement et hygiène mettez-vous actuellement en œuvre auprès de la communauté ?</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ما هي أنواع برامج المياه والصرف الصحي والنظافة التي تقدمونها حالياً للمجتمع؟</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>¿Qué tipo de programas de agua, saneamiento e higiene implementan actualmente para la comunidad?</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
           <t xml:space="preserve">What type of water, sanitation, and hygiene programming do you deliver to the community currently? </t>
@@ -1078,15 +1310,29 @@
           <t>targeting_criteria</t>
         </is>
       </c>
-      <c r="D17" s="2" t="n"/>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Quels sont vos critères de ciblage et de sélection pour les programmes mentionnés ci-dessus ?</t>
+        </is>
+      </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
           <t>(ménage ou communauté)</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ما هي معايير الاستهداف والاختيار للبرامج المذكورة أعلاه؟</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>(إما المنزل أو المجتمع)</t>
+          <t>(سواء على مستوى الأسرة أو المجتمع)</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>¿Cuáles son sus criterios de focalización y selección para los programas mencionados anteriormente?</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1121,7 +1367,21 @@
           <t>groups_limited_access</t>
         </is>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>Connaissez-vous des groupes au sein de la communauté qui rencontrent des difficultés pour accéder aux programmes ou s’y inscrire ?</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>هل تعرفون أي فئات داخل المجتمع تواجه صعوبات في الوصول إلى البرنامج أو التسجيل فيه؟</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>¿Conoce algún grupo dentro de la comunidad que tenga dificultades para acceder o registrarse en el programa?</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
           <t>Do you know of any groups within the community who have difficulties accessing/registering to the program?</t>
@@ -1144,7 +1404,21 @@
           <t>groups_limited_access_barriers</t>
         </is>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>Si oui, pouvez-vous nous parler des principaux obstacles ?</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>إذا كانت الإجابة نعم، هل يمكنكم إخبارنا بالعوائق الرئيسية؟</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Si la respuesta es sí, ¿puede contarnos cuáles son las principales barreras?</t>
+        </is>
+      </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
           <t>If yes, can you tell us about the main barriers?</t>
@@ -1167,7 +1441,21 @@
           <t>groups_limited_access_barriers_other</t>
         </is>
       </c>
-      <c r="D20" s="2" t="n"/>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Si autre, veuillez préciser :</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>إذا كانت الإجابة أخرى، يرجى التوضيح:</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Si es otro, por favor describa:</t>
+        </is>
+      </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">If other, please describe: </t>
@@ -1188,7 +1476,21 @@
           <t>main_wash_needs</t>
         </is>
       </c>
-      <c r="D21" s="5" t="n"/>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Parmi les communautés que vous atteignez grâce à vos programmes, quels sont les principaux besoins en eau, assainissement ou hygiène que vous observez ?</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>من بين المجتمعات التي تصلون إليها من خلال برامجكم، ما هي الاحتياجات الرئيسية في مجال المياه والصرف الصحي والنظافة التي تلاحظونها؟</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Entre las comunidades a las que llegan a través de sus programas, ¿cuáles son las principales necesidades de agua, saneamiento o higiene que observa?</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>Among the community, you’re reaching through your programs what are the main water, sanitation, or hygiene needs you observe?</t>
@@ -1209,7 +1511,21 @@
           <t>main_wash_challenges</t>
         </is>
       </c>
-      <c r="D22" s="5" t="n"/>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Quels sont les autres principaux défis que vous observez dans cette communauté ?</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ما هي التحديات الرئيسية الأخرى التي تلاحظونها في هذا المجتمع؟</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>¿Cuáles son los otros principales desafíos que observa en esta comunidad?</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>What are the other main challenges you observe in this community?</t>
@@ -1230,7 +1546,21 @@
           <t>main_wash_delivery_challenges_yn</t>
         </is>
       </c>
-      <c r="D23" s="3" t="n"/>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Rencontrez-vous actuellement des difficultés majeures pour fournir votre programme ou votre assistance à la population ciblée ?</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>هل تواجهون حالياً تحديات كبيرة في تقديم برنامجكم أو مساعدتكم إلى السكان المستهدفين؟</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>¿Actualmente enfrentan desafíos importantes para entregar su programa o asistencia a la población prevista?</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
           <t xml:space="preserve">Are you currently facing any major challenges in delivering your program/assistance to the intended population? </t>
@@ -1251,7 +1581,21 @@
           <t>main_wash_delivery_challenges_other</t>
         </is>
       </c>
-      <c r="D24" s="2" t="n"/>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Si autre, veuillez préciser :</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>إذا كانت الإجابة أخرى، يرجى التوضيح:</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Si es otro, por favor describa:</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
           <t xml:space="preserve">If other, please describe: </t>
@@ -1272,7 +1616,21 @@
           <t>main_wash_delivery_challenges_reason</t>
         </is>
       </c>
-      <c r="D25" s="3" t="n"/>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Si oui, veuillez décrire les principaux défis.</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>إذا كانت الإجابة نعم، يرجى وصف التحديات الرئيسية.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Si la respuesta es sí, describa los principales desafíos.</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
           <t xml:space="preserve">If yes, can you please describe the main challenges? </t>
@@ -1293,7 +1651,21 @@
           <t>shock_hazard_yn</t>
         </is>
       </c>
-      <c r="D26" s="3" t="n"/>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Y a-t-il eu récemment un choc ou un aléa ?</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>هل حدثت مؤخراً صدمة أو خطر؟</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>¿Ha habido recientemente un choque o peligro?</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
           <t xml:space="preserve">Has there been a recent shock or hazard? </t>
@@ -1314,7 +1686,21 @@
           <t>shock_hazard_adjust</t>
         </is>
       </c>
-      <c r="D27" s="3" t="n"/>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Si oui, comment avez-vous adapté vos programmes depuis [choc/aléa] ?</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>إذا كانت الإجابة نعم، كيف قمتم بتعديل برامجكم منذ [الصدمة/الخطر]؟</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Si la respuesta es sí, ¿cómo adaptaron sus programas desde [choque/peligro]?</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
           <t xml:space="preserve">If yes, how did you adjust your programming since [shock/hazard]? </t>
@@ -1335,7 +1721,21 @@
           <t>program_reach_impacted</t>
         </is>
       </c>
-      <c r="D28" s="2" t="n"/>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Ce changement affecte-t-il la couverture ou l’accès de certains groupes de la communauté ?</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>هل يؤثر هذا التغيير على الوصول أو التغطية لبعض فئات المجتمع؟</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>¿Este cambio afecta el alcance o el acceso de ciertos grupos de la comunidad?</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
           <t xml:space="preserve">Does this change impact the reach and/or access to certain groups of the community? </t>
@@ -1356,7 +1756,21 @@
           <t>program_reach_impacted_other</t>
         </is>
       </c>
-      <c r="D29" s="2" t="n"/>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Si autre, veuillez préciser :</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>إذا كانت الإجابة أخرى، يرجى التوضيح:</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Si es otro, por favor describa:</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
           <t xml:space="preserve">If other, please describe: </t>
@@ -1377,7 +1791,21 @@
           <t>program_reach_impacted_reason</t>
         </is>
       </c>
-      <c r="D30" s="3" t="n"/>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Si oui, veuillez décrire l’impact.</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>إذا كانت الإجابة نعم، يرجى وصف التأثير.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Si la respuesta es sí, describa el impacto.</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
           <t xml:space="preserve">If yes, can you please describe the impact? </t>
@@ -1398,7 +1826,21 @@
           <t>planned_programs_yn</t>
         </is>
       </c>
-      <c r="D31" s="2" t="n"/>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Avez-vous prévu de nouveaux programmes ou interventions d’assistance au cours des 3 prochains mois ?</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>هل لديكم أي برامج أو تدخلات مساعدة جديدة مخطط لها خلال الأشهر الثلاثة القادمة؟</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>¿Tienen previstos nuevos programas o entregas de asistencia en los próximos 3 meses?</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
           <t xml:space="preserve">Do you have any new programs or assistance delivery planned in the next 3 months? </t>
@@ -1419,7 +1861,21 @@
           <t>planned_programs_other</t>
         </is>
       </c>
-      <c r="D32" s="2" t="n"/>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Si autre, veuillez préciser :</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>إذا كانت الإجابة أخرى، يرجى التوضيح:</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Si es otro, por favor describa:</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
           <t xml:space="preserve">If other, please describe: </t>
@@ -1440,7 +1896,21 @@
           <t>planned_programs_describe</t>
         </is>
       </c>
-      <c r="D33" s="3" t="n"/>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Si oui, veuillez décrire les programmes prévus.</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>إذا كانت الإجابة نعم، يرجى وصف البرامج المخطط لها.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Si la respuesta es sí, describa los programas previstos.</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
           <t xml:space="preserve">If yes, can you please describe the planned programs? </t>
@@ -1461,7 +1931,21 @@
           <t>comments</t>
         </is>
       </c>
-      <c r="D34" s="2" t="n"/>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Autres remarques finales du personnel WASH ?</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>هل لدى موظفي برنامج المياه والصرف الصحي والنظافة أي ملاحظات ختامية أخرى؟</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>¿Algún otro comentario final del personal de WASH?</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
           <t>Any other closing remarks by the health care staff?</t>
@@ -1497,7 +1981,21 @@
           <t>comments_enum</t>
         </is>
       </c>
-      <c r="D36" s="2" t="n"/>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Observations finales de l’enquêteur ?</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>هل لدى الباحث الميداني أي ملاحظات نهائية؟</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>¿Observaciones finales del encuestador?</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
           <t>Any final observations from interviewer?</t>
@@ -1510,10 +2008,24 @@
     <row r="40"/>
     <row r="41"/>
     <row r="42">
-      <c r="D42" s="2" t="n"/>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1593,17 +2105,27 @@
     <row r="116"/>
     <row r="117"/>
     <row r="118">
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="C118" s="2" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="D119" s="2" t="n"/>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1972,12 +2494,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>رفض الإجابة</t>
+          <t>أفضل عدم الإجابة</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Se niega a responder</t>
+          <t>Prefiere no responder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2762,7 +3284,21 @@
           <t>water_point_rehab</t>
         </is>
       </c>
-      <c r="D33" s="8" t="n"/>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>Approvisionnement en eau – Réhabilitation des points d’eau</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>إمدادات المياه – إعادة تأهيل نقاط المياه</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Suministro de agua – Rehabilitación de puntos de agua</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
           <t>Water supply – Rehabilitation of water points</t>
@@ -2785,7 +3321,21 @@
           <t>water_trucking</t>
         </is>
       </c>
-      <c r="D34" s="8" t="n"/>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>Approvisionnement en eau – Transport d’eau par camion</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>إمدادات المياه – نقل المياه بالصهاريج</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Suministro de agua – Distribución de agua en camiones cisterna</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
           <t>Water supply – Water trucking</t>
@@ -2808,7 +3358,21 @@
           <t>water_treatment</t>
         </is>
       </c>
-      <c r="D35" s="8" t="n"/>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>Approvisionnement en eau – Traitement de l’eau</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>إمدادات المياه – معالجة المياه</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Suministro de agua – Tratamiento del agua</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>Water supply – Water treatment</t>
@@ -2831,7 +3395,21 @@
           <t>sanitation_emergency_latrine</t>
         </is>
       </c>
-      <c r="D36" s="8" t="n"/>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>Assainissement – Latrines d’urgence</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>الصرف الصحي – مراحيض طارئة</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Saneamiento – Letrinas de emergencia</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>Sanitation – Emergency Latrines</t>
@@ -2854,7 +3432,21 @@
           <t>sanitation_desludging</t>
         </is>
       </c>
-      <c r="D37" s="8" t="n"/>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>Assainissement – Vidange des latrines</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>الصرف الصحي – تفريغ/إزالة حمأة المراحيض</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Saneamiento – Vaciado de letrinas</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>Sanitation – Latrine Desludging</t>
@@ -2877,7 +3469,21 @@
           <t>sanitation_bathing</t>
         </is>
       </c>
-      <c r="D38" s="8" t="n"/>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>Assainissement – Installations de bain/douche</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>الصرف الصحي – مرافق الاستحمام</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Saneamiento – Instalaciones para bañarse</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>Sanitation – Bathing Facilities</t>
@@ -2900,7 +3506,21 @@
           <t>sanitation_solid_waste</t>
         </is>
       </c>
-      <c r="D39" s="8" t="n"/>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>Gestion des déchets solides – Collecte des déchets</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>إدارة النفايات الصلبة – جمع القمامة</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Gestión de residuos sólidos – Recolección de basura</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>Solid Waste Management – Garbage Collection</t>
@@ -2923,7 +3543,21 @@
           <t>hygiene_promotion</t>
         </is>
       </c>
-      <c r="D40" s="8" t="n"/>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>Promotion de l’hygiène</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>التوعية بالنظافة</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Promoción de higiene</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
           <t xml:space="preserve">Hygiene Promotion </t>
@@ -2946,7 +3580,21 @@
           <t>wash_nfi</t>
         </is>
       </c>
-      <c r="D41" s="8" t="n"/>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>Distribution d’articles non alimentaires WASH (savon, articles d’hygiène)</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>توزيع مواد غير غذائية خاصة بالمياه والصرف الصحي والنظافة (صابون، مواد نظافة)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Distribución de artículos no alimentarios WASH (jabón, artículos de higiene)</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
           <t>WASH NFI Distributions (Soap, Hygiene items)</t>
@@ -2969,7 +3617,21 @@
           <t>vector_control</t>
         </is>
       </c>
-      <c r="D42" s="8" t="n"/>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>Activités de lutte antivectorielle</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>أنشطة مكافحة النواقل</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Actividades de control de vectores</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr">
         <is>
           <t>Vector Control Activities</t>
@@ -3031,17 +3693,17 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Distance ou temps pour atteindre le lieu du programme/de l'aide</t>
+          <t>Distance ou temps nécessaire pour atteindre le lieu du programme ou de l’assistance</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>المسافة أو الوقت للوصول إلى موقع البرنامج</t>
+          <t>المسافة أو الوقت اللازم للوصول إلى موقع البرنامج أو المساعدة</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Distancia o tiempo para llegar al lugar del programa</t>
+          <t>Distancia o tiempo para llegar al lugar del programa o asistencia</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3066,7 +3728,21 @@
           <t>security</t>
         </is>
       </c>
-      <c r="D45" s="2" t="n"/>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Sécurité</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>الأمن</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Seguridad</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr">
         <is>
           <t>Security</t>
@@ -3126,7 +3802,21 @@
           <t>language</t>
         </is>
       </c>
-      <c r="D47" s="2" t="n"/>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Langue</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>اللغة</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Idioma</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr">
         <is>
           <t>Language</t>

--- a/inst/resources/tool_kii_wash_service_provider_iphra_v2.xlsx
+++ b/inst/resources/tool_kii_wash_service_provider_iphra_v2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1170" yWindow="720" windowWidth="14535" windowHeight="15480" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -628,42 +628,42 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>label::French (fr)</t>
+          <t>label::French</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>hint::French (fr)</t>
+          <t>hint::French</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>label::Arabic (ar)</t>
+          <t>label::Arabic</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>hint::Arabic (ar)</t>
+          <t>hint::Arabic</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>label::Spanish (sp)</t>
+          <t>label::Spanish</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>hint::Spanish (sp)</t>
+          <t>hint::Spanish</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>label::English (en)</t>
+          <t>label::English</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>hint::English (en)</t>
+          <t>hint::English</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
@@ -2002,130 +2002,50 @@
         </is>
       </c>
     </row>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
     <row r="42">
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-    </row>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
+          <t> </t>
+        </is>
+      </c>
+    </row>
     <row r="118">
       <c r="C118" s="2" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -2174,22 +2094,22 @@
       </c>
       <c r="D1" s="6" t="inlineStr">
         <is>
-          <t>label::French (fr)</t>
+          <t>label::French</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>label::Arabic (ar)</t>
+          <t>label::Arabic</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>label::Spanish (sp)</t>
+          <t>label::Spanish</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>label::English (en)</t>
+          <t>label::English</t>
         </is>
       </c>
     </row>
@@ -3920,7 +3840,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>English (en)</t>
+          <t>English</t>
         </is>
       </c>
     </row>
